--- a/OUTPUT_hormuz2026_reserve_intelligence.xlsx
+++ b/OUTPUT_hormuz2026_reserve_intelligence.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009E2B25"/>
+    </font>
+    <font>
+      <i val="1"/>
       <color rgb="009E2B25"/>
     </font>
     <font>
@@ -134,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,10 +174,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -248,154 +253,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Stock trajectory Feb-&gt;Jun 2026 (inflection: NOT yet turned)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Trajectory'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Trajectory'!$A$2:$A$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Trajectory'!$B$2:$B$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Trajectory'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Trajectory'!$A$2:$A$9</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Trajectory'!$C$2:$C$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2569,7 +2426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2744,9 +2601,15 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Inflection: NOT yet turned — OECD and US SPR both fall every print through 26 Jun.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2784,7 +2647,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
@@ -2806,7 +2669,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Reserve trajectory</t>
         </is>
@@ -2828,7 +2691,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Brent path</t>
         </is>
@@ -2850,7 +2713,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Restock</t>
         </is>
@@ -2872,7 +2735,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Reserve hard clock</t>
         </is>
@@ -2911,7 +2774,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>FOOTNOTES &amp; LIMITATIONS</t>
         </is>

--- a/OUTPUT_hormuz2026_reserve_intelligence.xlsx
+++ b/OUTPUT_hormuz2026_reserve_intelligence.xlsx
@@ -22,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="203">
   <si>
     <t>Hormuz 2026 — Crude Reserve, Redistribution &amp; Restocking Intelligence</t>
   </si>
   <si>
-    <t>As-of: 26 Jun 2026  |  War start 28 Feb 2026  |  Window T = 118 days  |  Brent $74.43  |  Hormuz contested-but-flowing ~4.8 mb/d</t>
+    <t>As-of: 26 Jun 2026  |  War start 28 Feb 2026  |  Window T = 118 days  |  Brent ~$72  |  Hormuz contested-but-flowing ~4.8 mb/d</t>
   </si>
   <si>
     <t>THESIS VERDICT: the 'reserves are conserved, just redistributed producer-side' hypothesis is REFUTED (strong form).</t>
@@ -54,10 +54,13 @@
     <t>CONFIDENCE LADDER:  Verified-official &gt; Inferred-triangulated &gt; Modelled-EST &gt; Absent('-').  A model is at most ONE source class.</t>
   </si>
   <si>
-    <t>CAVEAT (load-bearing): primary IEA OMR / EIA weekly hosts were proxy-blocked at run time, so many cells are WIRE-ATTRIBUTED</t>
-  </si>
-  <si>
-    <t>(one tier below Verified). Re-pull IEA/EIA directly before putting these decimals in front of a manager.</t>
+    <t>UPDATE 28 Jun 26: Consumer days + Key Indicators RE-VERIFIED vs Eurostat nrg_stk_oem, IEA oil-stocks tool &amp; EIA WPSR.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  EU stocks sit flat at the ~90d legal floor (net imports fell with stocks). India=EST; China/PH/ID/VN have no official series ('-').</t>
+  </si>
+  <si>
+    <t>CAVEAT: the analytic sheets (Ledger / Throughput / Trajectory / Scenarios) keep original wire-attribution — re-pull before external use.</t>
   </si>
   <si>
     <t>Sheets:  Consumer | Producer | Key Indicators | Ledger | Throughput | Trajectory | Scenarios | Footnotes</t>
@@ -111,97 +114,91 @@
     <t>Germany</t>
   </si>
   <si>
+    <t>Verified-official</t>
+  </si>
+  <si>
+    <t>Eurostat nrg_stk_oem, Dec-25-&gt;May-26 (~90d legal floor)</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Eurostat nrg_stk_oem, Dec-25-&gt;May-26</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Inferred-triangulated</t>
+  </si>
+  <si>
+    <t>GOV.UK/IEA/Al Jazeera, Mar 26</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Eurostat nrg_stk_oem (days-equiv), Dec-25-&gt;May-26</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>IEA oil-stocks tool, ~200d net-import, Mar-26</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>IEA oil-stocks tool, ~208d net-import, Mar-26; govt-only ~34d</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>No official net-import days series (NBS) — excluded</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
     <t>Modelled-EST</t>
   </si>
   <si>
-    <t>BMWE/EBV + IEA, 11 Mar 26 (before=110 imputed)</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Inferred-triangulated</t>
-  </si>
-  <si>
-    <t>IEA/Euronews/Eurostat, Apr 26</t>
-  </si>
-  <si>
-    <t>UK</t>
-  </si>
-  <si>
-    <t>GOV.UK/IEA/Al Jazeera, Mar 26</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>IEA Italy Oil Security / EU Dir 2009/119</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>CORES/IEA/Al Jazeera, Mar 26</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>IEA/COVA; net-exporter, metric undefined</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>IEA Poland Oil Security + model</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>S&amp;P/METI-ANRE, 9 May 26</t>
-  </si>
-  <si>
-    <t>South Korea</t>
-  </si>
-  <si>
-    <t>IEA tool/CSIS/Sedaily, May 26</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>Reuters-Kemp/EIA, 2026</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Min. Puri 76-80d, 8 Jun 26</t>
+    <t>EST: govt ~60d (BusinessToday May-26); SPR 9-10d; +commercial 40-45d (Kpler)</t>
   </si>
   <si>
     <t>Thailand</t>
   </si>
   <si>
-    <t>Thai Energy Ministry, 12 May 26 (on-ground ~56d)</t>
+    <t>Thai Energy Min, 1 May 26 (108d total; on-ground ~49d)</t>
   </si>
   <si>
     <t>Philippines</t>
   </si>
   <si>
-    <t>PH DOE OIMB weekly, 12 Jun 26</t>
+    <t>No comparable net-import days series (DOE demand-cover only) — excluded</t>
   </si>
   <si>
     <t>Indonesia</t>
   </si>
   <si>
-    <t>Jakarta Globe/ESDM, Jun 26 (capacity-capped ~25d)</t>
+    <t>No official net-import days series (ESDM) — excluded</t>
   </si>
   <si>
     <t>Vietnam</t>
   </si>
   <si>
-    <t>VietnamNet D-basis, May 26 (model ~16d; divergence kept)</t>
+    <t>No official days-of-cover series (MOIT) — excluded</t>
   </si>
   <si>
     <t>Export-cover days (deployable)</t>
@@ -288,10 +285,10 @@
     <t>~$120</t>
   </si>
   <si>
-    <t>$74.43</t>
-  </si>
-  <si>
-    <t>EIA RBRTE + Trading Economics</t>
+    <t>$72 (26 Jun)</t>
+  </si>
+  <si>
+    <t>Verified — Trading Economics/Fortune, 26 Jun 26 (low since 27 Feb)</t>
   </si>
   <si>
     <t>US SPR (mb)</t>
@@ -303,16 +300,16 @@
     <t>331 (19 Jun)</t>
   </si>
   <si>
-    <t>46.4% of ~714 nameplate; lowest since 1983</t>
+    <t>Verified — EIA WPSR; 46.4% of ~714 nameplate; lowest since 1983</t>
   </si>
   <si>
     <t>IEA collective release (mb)</t>
   </si>
   <si>
-    <t>400 (US share 172)</t>
-  </si>
-  <si>
-    <t>decided 11 Mar; ~186 executed by 19 Jun</t>
+    <t>400 auth / ~165 exec</t>
+  </si>
+  <si>
+    <t>auth 11 Mar; ~165 mb executed (EST) = OECD govt draw ~163 (IEA OMR Jun); US ~75-80 realized</t>
   </si>
   <si>
     <t>VLCC ($/day MEG-China)</t>
@@ -354,7 +351,7 @@
     <t>4.8</t>
   </si>
   <si>
-    <t>contested-but-flowing; 32% of prewar</t>
+    <t>Verified — Kpler/Reuters; contested-but-flowing; ~32% of prewar, recovering</t>
   </si>
   <si>
     <t>GLOBAL REDISTRIBUTION LEDGER — thesis test (all mb, window T=118d)</t>
@@ -710,7 +707,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -731,13 +728,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6D9C7"/>
+        <fgColor rgb="FFD6F0E0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBEED2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D9C7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -784,7 +787,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -808,13 +811,16 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1415,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="140.7109375" customWidth="1"/>
@@ -1487,21 +1493,26 @@
       <c r="A16" s="2"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="2"/>
+      <c r="A19" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1529,134 +1540,137 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="8">
         <v>0.08</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="B3" s="7">
+        <v>91</v>
+      </c>
+      <c r="C3" s="10">
+        <f>B3/30.44</f>
+        <v>3.0</v>
       </c>
       <c r="D3" s="7">
-        <v>99.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="E3" s="10">
         <f>D3/30.44</f>
-        <v>3.3</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>25</v>
+        <v>3.0</v>
+      </c>
+      <c r="F3" s="10">
+        <f>D3-B3</f>
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="11">
+        <f>(D3-B3)/B3</f>
+        <v>0.0</v>
       </c>
       <c r="H3" s="8">
         <v>0.05</v>
       </c>
       <c r="I3" s="10">
         <f>D3*(1-H3)</f>
-        <v>94.1</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>29</v>
+        <v>86.5</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="7">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C4" s="10">
         <f>B4/30.44</f>
-        <v>3.2</v>
+        <v>3.0</v>
       </c>
       <c r="D4" s="7">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E4" s="10">
         <f>D4/30.44</f>
-        <v>3.2</v>
+        <v>3.0</v>
       </c>
       <c r="F4" s="10">
         <f>D4-B4</f>
         <v>0.0</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <f>(D4-B4)/B4</f>
         <v>0.0</v>
       </c>
@@ -1665,10 +1679,10 @@
       </c>
       <c r="I4" s="10">
         <f>D4*(1-H4)</f>
-        <v>87.2</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>32</v>
+        <v>81.9</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>33</v>
@@ -1696,7 +1710,7 @@
         <f>D5-B5</f>
         <v>-14.0</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="11">
         <f>(D5-B5)/B5</f>
         <v>-0.1346153846153846</v>
       </c>
@@ -1708,47 +1722,50 @@
         <v>83.7</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="B6" s="7">
+        <v>92</v>
+      </c>
+      <c r="C6" s="10">
+        <f>B6/30.44</f>
+        <v>3.0</v>
       </c>
       <c r="D6" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" s="10">
         <f>D6/30.44</f>
         <v>3.0</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>25</v>
+      <c r="F6" s="10">
+        <f>D6-B6</f>
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="11">
+        <f>(D6-B6)/B6</f>
+        <v>0.0</v>
       </c>
       <c r="H6" s="8">
         <v>0.18</v>
       </c>
       <c r="I6" s="10">
         <f>D6*(1-H6)</f>
-        <v>73.8</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>32</v>
+        <v>75.4</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1756,14 +1773,14 @@
         <v>38</v>
       </c>
       <c r="B7" s="7">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="C7" s="10">
         <f>B7/30.44</f>
-        <v>3.9</v>
+        <v>3.0</v>
       </c>
       <c r="D7" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" s="10">
         <f>D7/30.44</f>
@@ -1771,101 +1788,109 @@
       </c>
       <c r="F7" s="10">
         <f>D7-B7</f>
-        <v>-29.0</v>
-      </c>
-      <c r="G7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="11">
         <f>(D7-B7)/B7</f>
-        <v>-0.24166666666666667</v>
+        <v>0.0</v>
       </c>
       <c r="H7" s="8">
         <v>0.06</v>
       </c>
       <c r="I7" s="10">
         <f>D7*(1-H7)</f>
-        <v>85.5</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>29</v>
+        <v>86.5</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
+      </c>
+      <c r="B8" s="7">
+        <v>90</v>
+      </c>
+      <c r="C8" s="10">
+        <f>B8/30.44</f>
+        <v>3.0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>90</v>
+      </c>
+      <c r="E8" s="10">
+        <f>D8/30.44</f>
+        <v>3.0</v>
+      </c>
+      <c r="F8" s="10">
+        <f>D8-B8</f>
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="11">
+        <f>(D8-B8)/B8</f>
+        <v>0.0</v>
       </c>
       <c r="H8" s="8">
         <v>0.06</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>26</v>
+      <c r="I8" s="10">
+        <f>D8*(1-H8)</f>
+        <v>84.6</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>41</v>
+      </c>
+      <c r="B9" s="7">
+        <v>90</v>
+      </c>
+      <c r="C9" s="10">
+        <f>B9/30.44</f>
+        <v>3.0</v>
       </c>
       <c r="D9" s="7">
-        <v>86.5</v>
+        <v>90</v>
       </c>
       <c r="E9" s="10">
         <f>D9/30.44</f>
-        <v>2.8</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>25</v>
+        <v>3.0</v>
+      </c>
+      <c r="F9" s="10">
+        <f>D9-B9</f>
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="11">
+        <f>(D9-B9)/B9</f>
+        <v>0.0</v>
       </c>
       <c r="H9" s="8">
         <v>0.13</v>
       </c>
       <c r="I9" s="10">
         <f>D9*(1-H9)</f>
-        <v>75.3</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>29</v>
+        <v>78.3</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" s="7">
         <v>200</v>
@@ -1875,37 +1900,37 @@
         <v>6.6</v>
       </c>
       <c r="D10" s="7">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E10" s="10">
         <f>D10/30.44</f>
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F10" s="10">
         <f>D10-B10</f>
-        <v>5.0</v>
-      </c>
-      <c r="G10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="11">
         <f>(D10-B10)/B10</f>
-        <v>0.025</v>
+        <v>0.0</v>
       </c>
       <c r="H10" s="8">
         <v>0.9</v>
       </c>
       <c r="I10" s="10">
         <f>D10*(1-H10)</f>
-        <v>20.5</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>32</v>
+        <v>20.0</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="7">
         <v>208</v>
@@ -1915,260 +1940,246 @@
         <v>6.8</v>
       </c>
       <c r="D11" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E11" s="10">
         <f>D11/30.44</f>
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="F11" s="10">
         <f>D11-B11</f>
-        <v>-3.0</v>
-      </c>
-      <c r="G11" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="11">
         <f>(D11-B11)/B11</f>
-        <v>-0.014423076923076924</v>
+        <v>0.0</v>
       </c>
       <c r="H11" s="8">
         <v>0.9</v>
       </c>
       <c r="I11" s="10">
         <f>D11*(1-H11)</f>
-        <v>20.5</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>32</v>
+        <v>20.8</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="7">
-        <v>122.5</v>
-      </c>
-      <c r="C12" s="10">
-        <f>B12/30.44</f>
-        <v>4.0</v>
-      </c>
-      <c r="D12" s="7">
-        <v>130</v>
-      </c>
-      <c r="E12" s="10">
-        <f>D12/30.44</f>
-        <v>4.3</v>
-      </c>
-      <c r="F12" s="10">
-        <f>D12-B12</f>
-        <v>7.5</v>
-      </c>
-      <c r="G12" s="12">
-        <f>(D12-B12)/B12</f>
-        <v>0.061224489795918366</v>
+        <v>46</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="H12" s="8">
         <v>0.46</v>
       </c>
-      <c r="I12" s="10">
-        <f>D12*(1-H12)</f>
-        <v>70.2</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>32</v>
+      <c r="I12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="7">
-        <v>74</v>
-      </c>
-      <c r="C13" s="10">
-        <f>B13/30.44</f>
-        <v>2.4</v>
+        <v>48</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D13" s="7">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E13" s="10">
         <f>D13/30.44</f>
-        <v>2.5</v>
-      </c>
-      <c r="F13" s="10">
-        <f>D13-B13</f>
         <v>2.0</v>
       </c>
-      <c r="G13" s="12">
-        <f>(D13-B13)/B13</f>
-        <v>0.02702702702702703</v>
+      <c r="F13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="H13" s="8">
         <v>0.3</v>
       </c>
       <c r="I13" s="10">
         <f>D13*(1-H13)</f>
-        <v>53.2</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>32</v>
+        <v>42.0</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E14" s="10">
         <f>D14/30.44</f>
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="8">
         <v>0.55</v>
       </c>
       <c r="I14" s="10">
         <f>D14*(1-H14)</f>
-        <v>52.6</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>32</v>
+        <v>48.6</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="7">
-        <v>46.47</v>
-      </c>
-      <c r="E15" s="10">
-        <f>D15/30.44</f>
-        <v>1.5</v>
+        <v>26</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" s="8">
         <v>0.95</v>
       </c>
-      <c r="I15" s="10">
-        <f>D15*(1-H15)</f>
-        <v>2.3</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>32</v>
+      <c r="I15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="7">
-        <v>21</v>
-      </c>
-      <c r="E16" s="10">
-        <f>D16/30.44</f>
-        <v>0.7</v>
+        <v>26</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="8">
         <v>0.2</v>
       </c>
-      <c r="I16" s="10">
-        <f>D16*(1-H16)</f>
-        <v>16.8</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>32</v>
+      <c r="I16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="7">
-        <v>40.3</v>
-      </c>
-      <c r="E17" s="10">
-        <f>D17/30.44</f>
-        <v>1.3</v>
+        <v>26</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H17" s="8">
         <v>0.88</v>
       </c>
-      <c r="I17" s="10">
-        <f>D17*(1-H17)</f>
-        <v>4.8</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>32</v>
+      <c r="I17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2194,42 +2205,42 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="J1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" s="7">
         <v>7.7</v>
@@ -2256,15 +2267,15 @@
         <v>2.3</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="7">
         <v>9</v>
@@ -2291,15 +2302,15 @@
         <v>1.4</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="7">
         <v>6</v>
@@ -2326,15 +2337,15 @@
         <v>1.45</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="7">
         <v>0.3</v>
@@ -2361,15 +2372,15 @@
         <v>1.5</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="7">
         <v>4.2</v>
@@ -2396,15 +2407,15 @@
         <v>2</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" s="7">
         <v>0</v>
@@ -2430,11 +2441,11 @@
       <c r="I7" s="7">
         <v>0.95</v>
       </c>
-      <c r="J7" s="11" t="s">
-        <v>29</v>
+      <c r="J7" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2455,121 +2466,121 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2589,90 +2600,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4" s="7">
         <v>615</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B5" s="7">
         <v>472</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" s="7">
         <v>410</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="7">
         <v>120</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" s="7">
         <v>775</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="15" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="15">
+      <c r="B10" s="16">
         <f>B7/B4</f>
         <v>0.1951219512195122</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11">
         <v>1200</v>
@@ -2680,31 +2691,31 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12">
         <v>495</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="14">
+      <c r="A13" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="15">
         <f>B5+B12+B6</f>
         <v>1377</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14">
         <f>B11-B13</f>
         <v>-177</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2724,95 +2735,95 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>132</v>
-      </c>
       <c r="C1" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B2" s="7">
         <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" s="7">
         <v>6.5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4" s="7">
         <v>4</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B5" s="7">
         <v>1.5</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="7">
         <v>0.2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B7" s="7">
         <v>0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B8" s="7">
         <v>4.8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B9" s="7">
         <v>4.5</v>
@@ -2840,21 +2851,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="7">
         <v>4100</v>
@@ -2863,12 +2874,12 @@
         <v>411</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B3" s="7">
         <v>4064</v>
@@ -2877,12 +2888,12 @@
         <v>411</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" s="7">
         <v>4000</v>
@@ -2891,12 +2902,12 @@
         <v>400.9</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="7">
         <v>3825</v>
@@ -2905,12 +2916,12 @@
         <v>384.1</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B6" s="7">
         <v>3787</v>
@@ -2919,12 +2930,12 @@
         <v>374.2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B7" s="7">
         <v>3711</v>
@@ -2933,12 +2944,12 @@
         <v>357.1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B8" s="7">
         <v>3598</v>
@@ -2947,12 +2958,12 @@
         <v>331.2</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9" s="7">
         <v>3560</v>
@@ -2961,12 +2972,12 @@
         <v>331.2</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2988,83 +2999,83 @@
     <row r="1" spans="1:4">
       <c r="A1" s="5"/>
       <c r="B1" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="15" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="14" t="s">
+      <c r="B2" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="15" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="14" t="s">
+      <c r="B3" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="15" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="14" t="s">
+      <c r="B4" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="15" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="14" t="s">
+      <c r="B5" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="15" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="14" t="s">
+      <c r="B6" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3082,7 +3093,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3090,57 +3101,57 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3148,7 +3159,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/OUTPUT_hormuz2026_reserve_intelligence.xlsx
+++ b/OUTPUT_hormuz2026_reserve_intelligence.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="207">
   <si>
     <t>Hormuz 2026 — Crude Reserve, Redistribution &amp; Restocking Intelligence</t>
   </si>
@@ -54,13 +54,16 @@
     <t>CONFIDENCE LADDER:  Verified-official &gt; Inferred-triangulated &gt; Modelled-EST &gt; Absent('-').  A model is at most ONE source class.</t>
   </si>
   <si>
-    <t>UPDATE 28 Jun 26: Consumer days + Key Indicators RE-VERIFIED vs Eurostat nrg_stk_oem, IEA oil-stocks tool &amp; EIA WPSR.</t>
+    <t>UPDATE 29 Jun 26: Consumer, Key Indicators, Producer, Trajectory &amp; Ledger RE-VERIFIED vs IEA OMR, EIA, Eurostat, Kpler &amp; Columbia CGEP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Verified = flow RATES + EIA weekly SPR series. Cumulative-mb ledger legs stay Inferred/EST; OECD weekly = Modelled-EST (no weekly OECD series).</t>
   </si>
   <si>
     <t xml:space="preserve">  EU stocks sit flat at the ~90d legal floor (net imports fell with stocks). India=EST; China/PH/ID/VN have no official series ('-').</t>
   </si>
   <si>
-    <t>CAVEAT: the analytic sheets (Ledger / Throughput / Trajectory / Scenarios) keep original wire-attribution — re-pull before external use.</t>
+    <t>CAVEAT: Throughput &amp; Scenarios sheets keep original wire-attribution — re-pull before external use.</t>
   </si>
   <si>
     <t>Sheets:  Consumer | Producer | Key Indicators | Ledger | Throughput | Trajectory | Scenarios | Footnotes</t>
@@ -228,37 +231,37 @@
     <t>Saudi Arabia</t>
   </si>
   <si>
-    <t>Argus/Bloomberg/Kayrros, Mar-Jun 26</t>
+    <t>Shut-in ~2.0 (Bloomberg 9 Mar, V); Yanbu bypass ~4.5 (Fortune 28 Mar, V); storage/floating in Gulf aggregate</t>
   </si>
   <si>
     <t>UAE</t>
   </si>
   <si>
-    <t>IEA OMR via The National, 24 Jun 26</t>
+    <t>Fujairah/ADCOP 1.62 mb/d Mar (Kpler, V); UAE shut-in within Gulf aggregate (EIA), no country figure</t>
   </si>
   <si>
     <t>Iran</t>
   </si>
   <si>
-    <t>Kpler/Al Jazeera, Jun 26</t>
+    <t>Storage ~74% Kharg (Columbia CGEP 28 Apr); floating ~127-147 mb (Kpler 24 Jun); shut-in ~2.5 (Goldman); no bypass (blockade 13 Apr)</t>
   </si>
   <si>
     <t>Iraq</t>
   </si>
   <si>
-    <t>Bloomberg/IEA OMR Apr/Basra Oil Co</t>
+    <t>Shut-in ~1.5 (Reuters 3 Mar, V); Kirkuk-Ceyhan ~0.25 (The National 16 Mar, V); tanks full (qual.)</t>
   </si>
   <si>
     <t>Kuwait</t>
   </si>
   <si>
-    <t>Bloomberg/Zawya/The National, Apr-Jun 26</t>
+    <t>Force majeure 20 Apr (WorldOil, V); shut-in mb/d inferred (no exact figure); no bypass line</t>
   </si>
   <si>
     <t>Qatar</t>
   </si>
   <si>
-    <t>EIA Qatar brief + OilPrice (downgraded)</t>
+    <t>Force majeure all exports 3 Mar (V); crude shut-in mb/d not individually published; no bypass</t>
   </si>
   <si>
     <t>Indicator</t>
@@ -366,31 +369,31 @@
     <t>Consumer / strategic stock draw</t>
   </si>
   <si>
-    <t>incl ~80 SPR + ~106 other-IEA strategic releases</t>
+    <t>EST cumulative; rate V: global -3.8 mb/d, OECD govt -163 mb (IEA OMR Jun); incl ~80 SPR realized</t>
   </si>
   <si>
     <t>Demand destruction</t>
   </si>
   <si>
-    <t>2Q26 deliveries -5 mb/d y/y (IEA OMR Jun)</t>
+    <t>rate V: 2Q26 deliveries -5 mb/d y/y (IEA OMR Jun); x~94d -&gt; EST cumulative</t>
   </si>
   <si>
     <t>Atlantic substitution (in)</t>
   </si>
   <si>
-    <t>rerouted East-of-Suez</t>
+    <t>rate V: +3.5 mb/d East-of-Suez (IEA OMR Jun) x118d=413; REALLOCATION not new supply (don't sum as absorption)</t>
   </si>
   <si>
     <t>Producer build (stranded)</t>
   </si>
   <si>
-    <t>floating ~100 + onshore ~20</t>
+    <t>EST: floating ~100 (Kpler ~67-100 stranded in Gulf, 24 Jun) + onshore ~20 modelled</t>
   </si>
   <si>
     <t>Foregone output (shut-in)</t>
   </si>
   <si>
-    <t>time-weighted ~700-850 (flat-rate point ~1,080)</t>
+    <t>EST; rate V: Gulf shut-in 7.5(Mar)-&gt;9.1(Apr) mb/d (MEES/EIA); time-weighted ~700-850 (flat ~1,080)</t>
   </si>
   <si>
     <t>rho = Producer build / Consumer draw</t>
@@ -477,52 +480,55 @@
     <t>27 Feb</t>
   </si>
   <si>
-    <t>Eve of war</t>
+    <t>Eve of war (SPR=EIA WCSSTUS1, V)</t>
   </si>
   <si>
     <t>13 Mar</t>
   </si>
   <si>
-    <t>IEA 400 mb release decided</t>
+    <t>IEA 400 mb release decided; SPR still untouched</t>
   </si>
   <si>
     <t>03 Apr</t>
   </si>
   <si>
-    <t>Global Apr draw -74 mb</t>
+    <t>First meaningful SPR draws begin</t>
   </si>
   <si>
     <t>08 May</t>
   </si>
   <si>
-    <t>Record weekly SPR draw 8.6 mb</t>
+    <t>SPR draw accelerating ~8-10 mb/wk</t>
   </si>
   <si>
     <t>15 May</t>
   </si>
   <si>
-    <t>All-time record weekly draw 9.92 mb</t>
+    <t>OECD GOVERNMENT stocks lowest since Dec 1990 (IEA)</t>
   </si>
   <si>
     <t>29 May</t>
   </si>
   <si>
-    <t>OECD govt stocks lowest since Dec 1990</t>
+    <t>SPR -8.0 mb on the week</t>
   </si>
   <si>
     <t>19 Jun</t>
   </si>
   <si>
-    <t>Lowest since 1983; ~46% of action drawn</t>
+    <t>Latest PUBLISHED EIA week; SPR -84 mb from prewar peak</t>
   </si>
   <si>
     <t>26 Jun</t>
   </si>
   <si>
-    <t>As-of; no build week yet</t>
-  </si>
-  <si>
-    <t>Inflection: NOT yet turned — both series fall every print through 26 Jun.</t>
+    <t>wk not yet published (EIA ~1 Jul); SPR carried flat at 19-Jun</t>
+  </si>
+  <si>
+    <t>SPR = EIA WCSSTUS1 weekly (Verified-official). OECD weekly = Modelled-EST off real IEA monthly anchors (no weekly OECD series).</t>
+  </si>
+  <si>
+    <t>Inflection: NOT yet turned — SPR falls every PUBLISHED print through 19 Jun; wk-ending 26 Jun not yet released by EIA.</t>
   </si>
   <si>
     <t>S1 — Reopen-fast</t>
@@ -624,7 +630,13 @@
     <t>Foregone output: flat 9.2 mb/d x118d = 1,080 mb indefensible vs flow data; time-weighted ~700-850 mb. REFUTED survives.</t>
   </si>
   <si>
-    <t>VERIFICATION NOT fully independent: IEA OMR / EIA weekly hosts were proxy-403-blocked; anchors WIRE-ATTRIBUTED (one tier below Verified).</t>
+    <t>RE-VERIFICATION 29 Jun 26: flow RATES confirmed vs IEA OMR Jun (global -3.8, demand -5, Atlantic +3.5 mb/d; OECD govt -163 mb) &amp; EIA WPSR (SPR 415-&gt;331). Cumulative-mb conversions remain analyst constructs (Inferred/EST).</t>
+  </si>
+  <si>
+    <t>Ledger tensions: 1,200 gap balances ONLY against flat-rate shut-in (1,080+120); with time-weighted shut-in (~775) effective gap is ~820-970. Observed net draw 495 runs ~10-15% hotter than IEA's literal 3.8 mb/d pace (~448). Atlantic substitution is reallocation, not a 3rd absorption term.</t>
+  </si>
+  <si>
+    <t>Producer storage-util % is country-specific ONLY for Iran (~74%, CGEP); others are 'tanks full' qualitative. Floating storage disaggregated only for Iran (Kpler); Kuwait/Qatar crude shut-in mb/d never individually published.</t>
   </si>
   <si>
     <t>Isolated red team raised 10 substantive attacks; all addressed in-run. Verify verdict: ship.</t>
@@ -915,28 +927,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>4100</c:v>
+                  <c:v>4095</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4064</c:v>
+                  <c:v>4035</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4000</c:v>
+                  <c:v>3955</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3825</c:v>
+                  <c:v>3800</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3787</c:v>
+                  <c:v>3755</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3711</c:v>
+                  <c:v>3680</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3598</c:v>
+                  <c:v>3595</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3560</c:v>
+                  <c:v>3555</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1003,13 +1015,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>411</c:v>
+                  <c:v>415.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>411</c:v>
+                  <c:v>415.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400.9</c:v>
+                  <c:v>413.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>384.1</c:v>
@@ -1421,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="140.7109375" customWidth="1"/>
@@ -1503,16 +1515,21 @@
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="2"/>
+      <c r="A20" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1540,77 +1557,77 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="8">
         <v>0.08</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="7">
         <v>91</v>
@@ -1642,15 +1659,15 @@
         <v>86.5</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="7">
         <v>92</v>
@@ -1682,15 +1699,15 @@
         <v>81.9</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="7">
         <v>104</v>
@@ -1722,15 +1739,15 @@
         <v>83.7</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="7">
         <v>92</v>
@@ -1762,15 +1779,15 @@
         <v>75.4</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7">
         <v>92</v>
@@ -1802,15 +1819,15 @@
         <v>86.5</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7">
         <v>90</v>
@@ -1842,15 +1859,15 @@
         <v>84.6</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="7">
         <v>90</v>
@@ -1882,15 +1899,15 @@
         <v>78.3</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="7">
         <v>200</v>
@@ -1922,15 +1939,15 @@
         <v>20.0</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="7">
         <v>208</v>
@@ -1962,56 +1979,56 @@
         <v>20.8</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" s="8">
         <v>0.46</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="7">
         <v>60</v>
@@ -2021,10 +2038,10 @@
         <v>2.0</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H13" s="8">
         <v>0.3</v>
@@ -2034,21 +2051,21 @@
         <v>42.0</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7">
         <v>108</v>
@@ -2058,10 +2075,10 @@
         <v>3.5</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H14" s="8">
         <v>0.55</v>
@@ -2071,115 +2088,115 @@
         <v>48.6</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" s="8">
         <v>0.95</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="8">
         <v>0.2</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H17" s="8">
         <v>0.88</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2205,42 +2222,42 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="7">
         <v>7.7</v>
@@ -2264,18 +2281,18 @@
         <v>4.5</v>
       </c>
       <c r="I2" s="7">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="7">
         <v>9</v>
@@ -2296,21 +2313,21 @@
         <v>0.9</v>
       </c>
       <c r="H3" s="7">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I3" s="7">
         <v>1.4</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="7">
         <v>6</v>
@@ -2319,7 +2336,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="7">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="E4" s="7">
         <v>0</v>
@@ -2328,24 +2345,24 @@
         <v>0</v>
       </c>
       <c r="G4" s="8">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
       <c r="H4" s="7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="7">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="7">
         <v>0.3</v>
@@ -2366,21 +2383,21 @@
         <v>0.95</v>
       </c>
       <c r="H5" s="7">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I5" s="7">
         <v>1.5</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="7">
         <v>4.2</v>
@@ -2407,15 +2424,15 @@
         <v>2</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="7">
         <v>0</v>
@@ -2442,10 +2459,10 @@
         <v>0.95</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2466,121 +2483,121 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2600,90 +2617,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="7">
         <v>615</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="7">
         <v>472</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" s="7">
         <v>410</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" s="7">
         <v>120</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" s="7">
         <v>775</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" s="16">
         <f>B7/B4</f>
         <v>0.1951219512195122</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11">
         <v>1200</v>
@@ -2691,7 +2708,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12">
         <v>495</v>
@@ -2699,7 +2716,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" s="15">
         <f>B5+B12+B6</f>
@@ -2708,14 +2725,14 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14">
         <f>B11-B13</f>
         <v>-177</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2735,95 +2752,95 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B2" s="7">
         <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="7">
         <v>6.5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" s="7">
         <v>4</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" s="7">
         <v>1.5</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B6" s="7">
         <v>0.2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B7" s="7">
         <v>0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B8" s="7">
         <v>4.8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B9" s="7">
         <v>4.5</v>
@@ -2840,7 +2857,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2851,133 +2868,138 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B2" s="7">
-        <v>4100</v>
+        <v>4095</v>
       </c>
       <c r="C2" s="7">
-        <v>411</v>
+        <v>415.4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B3" s="7">
-        <v>4064</v>
+        <v>4035</v>
       </c>
       <c r="C3" s="7">
-        <v>411</v>
+        <v>415.4</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B4" s="7">
-        <v>4000</v>
+        <v>3955</v>
       </c>
       <c r="C4" s="7">
-        <v>400.9</v>
+        <v>413.3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B5" s="7">
-        <v>3825</v>
+        <v>3800</v>
       </c>
       <c r="C5" s="7">
         <v>384.1</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B6" s="7">
-        <v>3787</v>
+        <v>3755</v>
       </c>
       <c r="C6" s="7">
         <v>374.2</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B7" s="7">
-        <v>3711</v>
+        <v>3680</v>
       </c>
       <c r="C7" s="7">
         <v>357.1</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B8" s="7">
-        <v>3598</v>
+        <v>3595</v>
       </c>
       <c r="C8" s="7">
         <v>331.2</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B9" s="7">
-        <v>3560</v>
+        <v>3555</v>
       </c>
       <c r="C9" s="7">
         <v>331.2</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>166</v>
+      <c r="A11" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2999,83 +3021,83 @@
     <row r="1" spans="1:4">
       <c r="A1" s="5"/>
       <c r="B1" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="15" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -3085,7 +3107,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="150.7109375" customWidth="1"/>
@@ -3093,7 +3115,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3101,65 +3123,75 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="3" t="s">
-        <v>200</v>
+      <c r="A12" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/OUTPUT_hormuz2026_reserve_intelligence.xlsx
+++ b/OUTPUT_hormuz2026_reserve_intelligence.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="209">
   <si>
     <t>Hormuz 2026 — Crude Reserve, Redistribution &amp; Restocking Intelligence</t>
   </si>
@@ -54,16 +54,16 @@
     <t>CONFIDENCE LADDER:  Verified-official &gt; Inferred-triangulated &gt; Modelled-EST &gt; Absent('-').  A model is at most ONE source class.</t>
   </si>
   <si>
-    <t>UPDATE 29 Jun 26: Consumer, Key Indicators, Producer, Trajectory &amp; Ledger RE-VERIFIED vs IEA OMR, EIA, Eurostat, Kpler &amp; Columbia CGEP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Verified = flow RATES + EIA weekly SPR series. Cumulative-mb ledger legs stay Inferred/EST; OECD weekly = Modelled-EST (no weekly OECD series).</t>
+    <t>UPDATE 29 Jun 26: ALL 9 sheets reviewed/RE-VERIFIED vs IEA OMR, EIA, Eurostat, Kpler &amp; Columbia CGEP (Consumer, Key Ind, Producer, Trajectory, Ledger, Throughput, Scenarios).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Verified = flow RATES + EIA weekly SPR series + bypass/throughput. Cumulative-mb ledger legs stay Inferred/EST; OECD weekly = Modelled-EST (no weekly series).</t>
   </si>
   <si>
     <t xml:space="preserve">  EU stocks sit flat at the ~90d legal floor (net imports fell with stocks). India=EST; China/PH/ID/VN have no official series ('-').</t>
   </si>
   <si>
-    <t>CAVEAT: Throughput &amp; Scenarios sheets keep original wire-attribution — re-pull before external use.</t>
+    <t>CAVEAT: Scenarios are forward PROJECTIONS (Modelled-EST), not data; price anchors map to the named bench. Re-pull primary IEA/EIA before quoting any decimal externally.</t>
   </si>
   <si>
     <t>Sheets:  Consumer | Producer | Key Indicators | Ledger | Throughput | Trajectory | Scenarios | Footnotes</t>
@@ -426,43 +426,43 @@
     <t>Hormuz normal crude exit</t>
   </si>
   <si>
-    <t>prewar baseline</t>
+    <t>prewar baseline (EIA, V)</t>
   </si>
   <si>
     <t>Bypass ceiling</t>
   </si>
   <si>
-    <t>port-gated, not pipeline-gated</t>
+    <t>realized ~5.7 mb/d; port-gated not pipeline-gated (V)</t>
   </si>
   <si>
     <t xml:space="preserve">  Yanbu / Petroline (Red Sea)</t>
   </si>
   <si>
-    <t>~70% of all bypass; port-limited</t>
+    <t>Fortune 28 Mar (V); 7 mb/d pipe but Yanbu port caps ~4; ~70% of bypass</t>
   </si>
   <si>
     <t xml:space="preserve">  Fujairah / ADCOP (Gulf of Oman)</t>
   </si>
   <si>
-    <t>true bypass; terminal at strait mouth</t>
+    <t>Kpler 1.62 mb/d Mar (V); true bypass at strait mouth</t>
   </si>
   <si>
     <t xml:space="preserve">  Kirkuk-Ceyhan (Med)</t>
   </si>
   <si>
-    <t>north-only; near-zero true relief</t>
+    <t>The National 16 Mar (V); north-only, near-zero true relief</t>
   </si>
   <si>
     <t xml:space="preserve">  Goreh-Jask</t>
   </si>
   <si>
-    <t>idle since 2024</t>
+    <t>idle since 2024 (V)</t>
   </si>
   <si>
     <t>Hormuz actual flow (now)</t>
   </si>
   <si>
-    <t>contested-but-flowing</t>
+    <t>Kpler/Reuters late-Jun (V); contested-but-flowing, recovering</t>
   </si>
   <si>
     <t>Stranded (end-state)</t>
@@ -567,13 +567,13 @@
     <t>Brent</t>
   </si>
   <si>
-    <t>$60-68</t>
-  </si>
-  <si>
-    <t>$70-85 range, headline spikes decay</t>
-  </si>
-  <si>
-    <t>Re-rate toward/above $120</t>
+    <t>$64-75 (JPM/GS '27 bench)</t>
+  </si>
+  <si>
+    <t>$70-85; now ~$72 (deal-holds bench)</t>
+  </si>
+  <si>
+    <t>$105-130 (Rapidan ~$130 peak; RBC)</t>
   </si>
   <si>
     <t>Restock</t>
@@ -598,6 +598,12 @@
   </si>
   <si>
     <t>US SPR-&gt;150 mb ~5 Nov 26; OECD action ~11 Nov 26</t>
+  </si>
+  <si>
+    <t>These are forward PROJECTIONS (Modelled-EST), not verified data. Price anchors map to the named bench:</t>
+  </si>
+  <si>
+    <t>JPMorgan ~$64 (2027) / Goldman ~$75 / Morgan Stanley ~$80 (deal-holds); Rapidan ~$130 peak / RBC 'risk underpriced' (reclose). Reserve hard-clock dates are EST extrapolations of the acute draw rate.</t>
   </si>
   <si>
     <t>FOOTNOTES &amp; LIMITATIONS</t>
@@ -2846,7 +2852,7 @@
         <v>4.5</v>
       </c>
       <c r="C9" s="6">
-        <f> 15 - bypass 5.7 - Hormuz 4.8</f>
+        <f> 15 - bypass 5.7 - Hormuz 4.8 (derived)</f>
         <v>0</v>
       </c>
     </row>
@@ -3010,7 +3016,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3098,6 +3104,16 @@
       </c>
       <c r="D6" s="6" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3115,7 +3131,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3123,67 +3139,67 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -3191,7 +3207,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
